--- a/Assessment Questions/CDE/DATA ENGINEERING FOUNDATION/Data Integrity and Privacy/Various aspects of Data privacy/Data Privacy Aspects.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING FOUNDATION/Data Integrity and Privacy/Various aspects of Data privacy/Data Privacy Aspects.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Privacy Aspects" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,12 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -481,12 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -518,12 +508,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -555,12 +540,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -592,12 +572,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -629,12 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -666,12 +636,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -703,12 +668,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -740,12 +700,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -777,12 +732,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -814,12 +764,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -851,12 +796,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -888,12 +828,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -925,12 +860,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -962,12 +892,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -999,12 +924,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1036,12 +956,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1073,12 +988,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1020,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1052,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1084,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
